--- a/data/trans_camb/P2C_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 16,28</t>
+          <t>2,97; 16,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 16,71</t>
+          <t>2,93; 16,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-32,65; -21,99</t>
+          <t>-32,29; -22,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,96; 18,89</t>
+          <t>5,76; 18,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 5,7</t>
+          <t>-7,92; 5,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,66; -30,84</t>
+          <t>-40,99; -30,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 15,69</t>
+          <t>6,08; 15,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 8,43</t>
+          <t>-0,74; 8,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-35,42; -28,06</t>
+          <t>-35,72; -28,09</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,84; 50,62</t>
+          <t>7,49; 51,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 51,14</t>
+          <t>7,94; 50,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-82,41; -67,69</t>
+          <t>-82,05; -67,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,7; 43,3</t>
+          <t>11,41; 43,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 12,91</t>
+          <t>-16,1; 12,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,83; -71,25</t>
+          <t>-82,0; -70,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,23; 39,57</t>
+          <t>13,84; 39,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 21,72</t>
+          <t>-1,69; 21,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-80,7; -71,8</t>
+          <t>-80,84; -71,92</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 17,81</t>
+          <t>5,8; 16,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 13,89</t>
+          <t>2,02; 13,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-35,24; -24,64</t>
+          <t>-35,22; -24,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,3; 18,7</t>
+          <t>8,89; 19,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 12,23</t>
+          <t>0,82; 11,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,47; -27,66</t>
+          <t>-36,84; -27,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,65; 16,33</t>
+          <t>8,73; 16,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 11,35</t>
+          <t>3,58; 11,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-35,91; -27,94</t>
+          <t>-36,6; -28,03</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,41; 53,24</t>
+          <t>14,77; 48,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 40,17</t>
+          <t>4,82; 39,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,86; -69,37</t>
+          <t>-88,85; -69,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,94; 40,83</t>
+          <t>17,11; 41,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 26,84</t>
+          <t>1,21; 25,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,53; -60,45</t>
+          <t>-70,45; -59,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,01; 39,24</t>
+          <t>19,3; 41,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,84; 27,58</t>
+          <t>7,97; 27,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-81,08; -67,05</t>
+          <t>-81,71; -67,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,03; 22,22</t>
+          <t>7,88; 21,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 16,36</t>
+          <t>2,3; 16,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-36,05; -25,12</t>
+          <t>-35,72; -25,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,12; 30,46</t>
+          <t>17,55; 30,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 17,01</t>
+          <t>4,54; 17,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,46; 18,45</t>
+          <t>-34,74; 20,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,63; 24,68</t>
+          <t>15,2; 24,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 15,11</t>
+          <t>5,92; 15,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-32,29; 4,14</t>
+          <t>-32,87; 5,28</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,47; 70,0</t>
+          <t>19,21; 67,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,46; 50,25</t>
+          <t>5,83; 50,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-87,78; -74,88</t>
+          <t>-87,8; -75,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36,48; 75,31</t>
+          <t>36,91; 75,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,67; 42,24</t>
+          <t>9,46; 42,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,17; 45,49</t>
+          <t>-77,09; 52,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,45; 65,25</t>
+          <t>34,74; 63,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,86; 39,26</t>
+          <t>14,43; 40,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-79,46; 10,71</t>
+          <t>-79,8; 15,82</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,72; 18,98</t>
+          <t>7,49; 19,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 8,56</t>
+          <t>-3,6; 8,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-35,14; -25,79</t>
+          <t>-34,6; -25,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,02; 19,82</t>
+          <t>9,04; 19,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 9,35</t>
+          <t>-2,27; 8,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-40,34; -31,86</t>
+          <t>-40,93; -32,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,68; 17,81</t>
+          <t>9,42; 16,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 7,15</t>
+          <t>-0,81; 7,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-36,79; -30,29</t>
+          <t>-36,81; -30,81</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,09; 55,21</t>
+          <t>18,28; 59,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 24,62</t>
+          <t>-8,55; 25,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-84,75; -74,84</t>
+          <t>-84,59; -74,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,2; 47,75</t>
+          <t>19,38; 48,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 22,76</t>
+          <t>-4,75; 21,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-85,43; -77,01</t>
+          <t>-85,46; -76,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,73; 44,64</t>
+          <t>21,33; 42,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 18,1</t>
+          <t>-1,78; 18,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-83,82; -77,59</t>
+          <t>-84,03; -77,67</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,57; 15,35</t>
+          <t>9,39; 15,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,02; 10,25</t>
+          <t>4,17; 10,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-32,18; -26,61</t>
+          <t>-31,87; -26,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,93; 18,71</t>
+          <t>12,66; 18,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,14; 8,1</t>
+          <t>1,98; 8,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-35,15; -13,5</t>
+          <t>-34,97; -13,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,69; 16,22</t>
+          <t>12,01; 16,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,21; 8,7</t>
+          <t>3,73; 8,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-32,69; -19,94</t>
+          <t>-32,76; -21,31</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>24,91; 43,07</t>
+          <t>24,23; 43,04</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10,66; 29,1</t>
+          <t>10,93; 28,89</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,52; -75,76</t>
+          <t>-83,61; -75,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27,3; 42,07</t>
+          <t>26,64; 41,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,33; 17,99</t>
+          <t>4,12; 18,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-75,41; -29,28</t>
+          <t>-75,25; -29,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,07; 40,0</t>
+          <t>28,2; 40,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9,75; 21,24</t>
+          <t>8,52; 20,02</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-77,62; -48,08</t>
+          <t>-77,41; -50,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Habitat-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-35,83</t>
+          <t>-34,81</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-31,93</t>
+          <t>-31,44</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 16,59</t>
+          <t>3,21; 15,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 16,2</t>
+          <t>2,59; 16,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-32,29; -22,07</t>
+          <t>-32,96; -22,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 18,39</t>
+          <t>6,01; 18,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 5,69</t>
+          <t>-7,53; 5,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,99; -30,94</t>
+          <t>-39,57; -29,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,08; 15,46</t>
+          <t>5,92; 15,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 8,62</t>
+          <t>-1,0; 8,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-35,72; -28,09</t>
+          <t>-34,89; -27,86</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-76,0%</t>
+          <t>-75,99%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-76,76%</t>
+          <t>-74,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-76,48%</t>
+          <t>-75,31%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 51,59</t>
+          <t>7,76; 49,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,94; 50,81</t>
+          <t>6,49; 49,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-82,05; -67,86</t>
+          <t>-82,52; -67,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,41; 43,05</t>
+          <t>12,04; 43,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 12,87</t>
+          <t>-14,37; 13,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,0; -70,92</t>
+          <t>-78,97; -68,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,84; 39,69</t>
+          <t>13,77; 39,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 21,49</t>
+          <t>-2,16; 21,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-80,84; -71,92</t>
+          <t>-79,2; -70,62</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-29,29</t>
+          <t>-25,94</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-31,9</t>
+          <t>-31,52</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-31,34</t>
+          <t>-28,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,8; 16,86</t>
+          <t>6,23; 17,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 13,8</t>
+          <t>2,0; 14,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-35,22; -24,75</t>
+          <t>-30,56; -21,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,89; 19,0</t>
+          <t>8,34; 19,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 11,53</t>
+          <t>1,08; 12,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,84; -27,69</t>
+          <t>-36,05; -27,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,73; 16,95</t>
+          <t>8,58; 16,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 11,43</t>
+          <t>3,65; 11,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-36,6; -28,03</t>
+          <t>-32,23; -25,93</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-77,72%</t>
+          <t>-68,82%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-65,5%</t>
+          <t>-64,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-72,07%</t>
+          <t>-66,67%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,77; 48,74</t>
+          <t>15,14; 49,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 39,24</t>
+          <t>5,11; 40,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-88,85; -69,73</t>
+          <t>-75,08; -61,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,11; 41,94</t>
+          <t>16,53; 42,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 25,24</t>
+          <t>2,01; 26,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,45; -59,61</t>
+          <t>-69,46; -58,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,3; 41,18</t>
+          <t>19,13; 41,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,97; 27,85</t>
+          <t>7,88; 27,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-81,71; -67,11</t>
+          <t>-70,87; -62,46</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-29,82</t>
+          <t>-29,52</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-13,17</t>
+          <t>-31,58</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-20,12</t>
+          <t>-30,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,88; 21,76</t>
+          <t>8,71; 21,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 16,46</t>
+          <t>3,19; 16,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-35,72; -25,12</t>
+          <t>-34,58; -24,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,55; 30,34</t>
+          <t>16,72; 29,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 17,05</t>
+          <t>4,53; 17,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 20,96</t>
+          <t>-36,54; -26,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,2; 24,42</t>
+          <t>14,96; 24,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,92; 15,12</t>
+          <t>5,71; 15,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-32,87; 5,28</t>
+          <t>-34,71; -27,32</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-82,58%</t>
+          <t>-81,75%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-30,18%</t>
+          <t>-72,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-50,07%</t>
+          <t>-76,76%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,21; 67,27</t>
+          <t>22,19; 67,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,83; 50,29</t>
+          <t>8,22; 50,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-87,8; -75,67</t>
+          <t>-86,94; -74,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36,91; 75,78</t>
+          <t>35,53; 74,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,46; 42,49</t>
+          <t>9,29; 42,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,09; 52,01</t>
+          <t>-77,61; -66,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,74; 63,97</t>
+          <t>34,8; 64,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,43; 40,84</t>
+          <t>13,37; 41,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-79,8; 15,82</t>
+          <t>-80,91; -72,14</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-30,24</t>
+          <t>-29,78</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-36,1</t>
+          <t>-34,64</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-33,68</t>
+          <t>-32,7</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,49; 19,89</t>
+          <t>7,36; 19,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 8,79</t>
+          <t>-3,03; 8,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-34,6; -25,22</t>
+          <t>-34,24; -25,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,04; 19,71</t>
+          <t>8,72; 19,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 8,89</t>
+          <t>-1,7; 9,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-40,93; -32,21</t>
+          <t>-38,8; -30,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,42; 16,91</t>
+          <t>9,75; 17,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 7,33</t>
+          <t>-0,93; 7,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-36,81; -30,81</t>
+          <t>-35,6; -29,66</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-80,46%</t>
+          <t>-79,23%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-80,93%</t>
+          <t>-77,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-80,86%</t>
+          <t>-78,5%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,28; 59,35</t>
+          <t>17,58; 55,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 25,4</t>
+          <t>-7,67; 25,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-84,59; -74,1</t>
+          <t>-83,83; -73,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,38; 48,1</t>
+          <t>18,17; 46,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 21,09</t>
+          <t>-3,63; 22,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-85,46; -76,94</t>
+          <t>-81,31; -73,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,33; 42,73</t>
+          <t>22,64; 44,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 18,58</t>
+          <t>-2,07; 18,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-84,03; -77,67</t>
+          <t>-81,16; -75,15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-29,23</t>
+          <t>-28,09</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-29,38</t>
+          <t>-33,14</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-29,57</t>
+          <t>-30,98</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,39; 15,38</t>
+          <t>9,5; 15,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,17; 10,35</t>
+          <t>4,16; 10,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-31,87; -26,56</t>
+          <t>-30,72; -25,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,66; 18,2</t>
+          <t>12,7; 18,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,98; 8,07</t>
+          <t>2,49; 8,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-34,97; -13,19</t>
+          <t>-35,41; -30,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,01; 16,18</t>
+          <t>11,99; 16,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,18</t>
+          <t>4,15; 8,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-32,76; -21,31</t>
+          <t>-32,67; -29,27</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-79,08%</t>
+          <t>-76,01%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-63,86%</t>
+          <t>-72,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-70,56%</t>
+          <t>-73,94%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>24,23; 43,04</t>
+          <t>25,1; 44,59</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10,93; 28,89</t>
+          <t>10,56; 28,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,61; -75,7</t>
+          <t>-79,08; -73,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26,64; 41,24</t>
+          <t>26,82; 41,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,12; 18,1</t>
+          <t>5,18; 18,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-75,25; -29,03</t>
+          <t>-74,48; -69,47</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,2; 40,1</t>
+          <t>27,87; 39,88</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8,52; 20,02</t>
+          <t>9,74; 20,92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-77,41; -50,83</t>
+          <t>-75,69; -71,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
